--- a/design/怪物表.xlsx
+++ b/design/怪物表.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -9,10 +9,11 @@
   <sheets>
     <sheet name="怪物|Monster" sheetId="1" r:id="rId1"/>
     <sheet name="怪物技能|MonsterSkill" sheetId="2" r:id="rId2"/>
+    <sheet r:id="rId6" name="招式|Attack" sheetId="3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
@@ -221,14 +222,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="58">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -427,8 +428,169 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF12283F"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF79511F"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF79511F"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF202C3A"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF20364D"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF20364D"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF20364D"/>
+      <name val="Microsoft YaHei"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="75">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -651,8 +813,193 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9CEE3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF0CF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD3E7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -825,8 +1172,146 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
+    <border>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7EFF7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7EFF7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7EFF7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7EFF7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color theme="4" tint="0.49998"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="100">
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -975,8 +1460,156 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="34" fillId="0" borderId="14" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="34" fillId="0" borderId="14" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="0" borderId="14" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="34" fillId="0" borderId="14" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="34" fillId="0" borderId="14" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="43" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="44" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="45" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="45" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="46" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="47" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="48" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="49" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="50" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="51" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="52" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="53" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="54" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="55" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="56" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="57" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="58" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="59" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="60" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="61" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="62" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="63" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="64" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="65" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="66" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="67" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="68" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="69" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="70" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="71" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="72" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="73" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="14"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1037,6 +1670,85 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="99"/>
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="15" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="16" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="14" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="17" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="18" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="14" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="32" fillId="40" borderId="14" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="32" fillId="41" borderId="14" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="28" fillId="0" borderId="14" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" xfId="99" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="19" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="42" borderId="19" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="19" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="42" borderId="19" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="32" fillId="40" borderId="19" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="40" borderId="19" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="32" fillId="41" borderId="19" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="41" borderId="19" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="33" fillId="0" borderId="19" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="19" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="74" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="74" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="74" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="74" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="74" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="74" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="56" fillId="74" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="74" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="56" fillId="74" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="74" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="74" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="74" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1307,7 +2019,7 @@
     </tableStyle>
   </tableStyles>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
@@ -1511,7 +2223,7 @@
   <sheetPr>
     <tabColor rgb="FF577A9A"/>
   </sheetPr>
-  <dimension ref="A1:Q504"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="20" style="12" customWidth="1"/>
@@ -1524,6 +2236,8 @@
     <col min="13" max="14" width="13.5" style="12" customWidth="1"/>
     <col min="15" max="15" width="9.5" style="12" customWidth="1"/>
     <col min="17" max="17" width="55" customWidth="1"/>
+    <col min="17" max="17" width="22" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="22" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:17">
@@ -1572,8 +2286,14 @@
       <c r="O1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="4" t="s">
-        <v>15</v>
+      <c r="P1" s="47" t="str">
+        <v>DEMO招式配置ID</v>
+      </c>
+      <c r="Q1" s="54" t="str">
+        <v>掉落组ID</v>
+      </c>
+      <c r="U1" t="str">
+        <v>配置模板 · 待接入</v>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:17">
@@ -1622,8 +2342,14 @@
       <c r="O2" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="8" t="s">
-        <v>18</v>
+      <c r="P2" s="47" t="str">
+        <v>int32</v>
+      </c>
+      <c r="Q2" s="55" t="str">
+        <v>int32</v>
+      </c>
+      <c r="U2" t="str">
+        <v>详见《配置表填写说明.md》</v>
       </c>
     </row>
     <row r="3" ht="29" customHeight="1" spans="1:17">
@@ -1672,7 +2398,12 @@
       <c r="O3" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" s="8"/>
+      <c r="P3" s="47" t="str">
+        <v>AttackIdx</v>
+      </c>
+      <c r="Q3" s="55" t="str">
+        <v>DropIdx</v>
+      </c>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:17">
       <c r="A4" s="15" t="s">
@@ -1720,7 +2451,12 @@
       <c r="O4" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="Q4" s="8"/>
+      <c r="P4" s="47" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="Q4" s="55" t="str">
+        <v>server/client</v>
+      </c>
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:17">
       <c r="A5" s="17">
@@ -1758,8 +2494,9 @@
       <c r="O5" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="Q5" s="8" t="s">
-        <v>39</v>
+      <c r="Q5" s="29"/>
+      <c r="U5" t="str">
+        <v>资源空值表示待美术交付；新增数值为示例。</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1" spans="1:17">
@@ -1941,38 +2678,106 @@
       <c r="O11" s="18"/>
     </row>
     <row r="12" spans="1:17">
-      <c r="A12" s="21"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22"/>
+      <c r="A12" s="42" t="n">
+        <v>1002</v>
+      </c>
+      <c r="B12" s="43" t="str">
+        <v>拾荒兽（DEMO）</v>
+      </c>
+      <c r="C12" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="42" t="n">
+        <v>600</v>
+      </c>
+      <c r="E12" s="42" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F12" s="42" t="n">
+        <v>60</v>
+      </c>
+      <c r="G12" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="42" t="n">
+        <v>35</v>
+      </c>
+      <c r="K12" s="42" t="n">
+        <v>35</v>
+      </c>
+      <c r="L12" s="42" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M12" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="43" t="str"/>
+      <c r="P12" t="n">
+        <v>1002</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:17">
-      <c r="A13" s="21"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
+      <c r="A13" s="42" t="n">
+        <v>1003</v>
+      </c>
+      <c r="B13" s="43" t="str">
+        <v>铁甲首领（DEMO）</v>
+      </c>
+      <c r="C13" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E13" s="42" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F13" s="42" t="n">
+        <v>240</v>
+      </c>
+      <c r="G13" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="42" t="n">
+        <v>25</v>
+      </c>
+      <c r="K13" s="42" t="n">
+        <v>25</v>
+      </c>
+      <c r="L13" s="42" t="n">
+        <v>7000</v>
+      </c>
+      <c r="M13" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="43" t="str"/>
+      <c r="P13" t="n">
+        <v>1003</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="21"/>
@@ -14532,4 +15337,160 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="47" t="str">
+        <v>招式ID</v>
+      </c>
+      <c r="B1" s="47" t="str">
+        <v>名称</v>
+      </c>
+      <c r="C1" s="47" t="str">
+        <v>攻击范围（毫米）</v>
+      </c>
+      <c r="D1" s="47" t="str">
+        <v>伤害</v>
+      </c>
+      <c r="E1" s="47" t="str">
+        <v>冷却（Tick）</v>
+      </c>
+      <c r="F1" s="47" t="str">
+        <v>前摇（Tick）</v>
+      </c>
+      <c r="G1" s="47" t="str">
+        <v>后摇（Tick）</v>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="47" t="str">
+        <v>int32</v>
+      </c>
+      <c r="B2" s="47" t="str">
+        <v>string</v>
+      </c>
+      <c r="C2" s="47" t="str">
+        <v>int32</v>
+      </c>
+      <c r="D2" s="47" t="str">
+        <v>int32</v>
+      </c>
+      <c r="E2" s="47" t="str">
+        <v>int32</v>
+      </c>
+      <c r="F2" s="47" t="str">
+        <v>int32</v>
+      </c>
+      <c r="G2" s="47" t="str">
+        <v>int32</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="47" t="str">
+        <v>AttackIdx</v>
+      </c>
+      <c r="B3" s="47" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C3" s="47" t="str">
+        <v>Range</v>
+      </c>
+      <c r="D3" s="47" t="str">
+        <v>Damage</v>
+      </c>
+      <c r="E3" s="47" t="str">
+        <v>CooldownTicks</v>
+      </c>
+      <c r="F3" s="47" t="str">
+        <v>WindupTicks</v>
+      </c>
+      <c r="G3" s="47" t="str">
+        <v>RecoveryTicks</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="47" t="str">
+        <v>server/client/key</v>
+      </c>
+      <c r="B4" s="47" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="C4" s="47" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="D4" s="47" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="E4" s="47" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="F4" s="47" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="G4" s="47" t="str">
+        <v>server/client</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" t="n">
+        <v>1002</v>
+      </c>
+      <c r="B5" t="str">
+        <v>普通近战</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" t="n">
+        <v>1003</v>
+      </c>
+      <c r="B6" t="str">
+        <v>首领重击</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" t="n">
+        <v>90</v>
+      </c>
+      <c r="F6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/design/怪物表.xlsx
+++ b/design/怪物表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\聚光灯\Hunter\design\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <ns1:AlternateContent>
+    <ns1:Choice Requires="x15">
+      <ns2:absPath url="E:\聚光灯\Hunter\design\"/>
+    </ns1:Choice>
+  </ns1:AlternateContent>
   <bookViews>
     <workbookView windowWidth="24750" windowHeight="12060"/>
   </bookViews>
@@ -15,19 +15,22 @@
     <sheet name="怪物|Monster" sheetId="1" r:id="rId1"/>
     <sheet name="怪物技能|MonsterSkill" sheetId="2" r:id="rId2"/>
     <sheet name="招式|Attack" sheetId="3" r:id="rId3"/>
+    <sheet name="怪物行为|MonsterAi" sheetId="4" r:id="rIdCfg4"/>
+    <sheet name="能力|Ability" sheetId="5" r:id="rIdCfg5"/>
+    <sheet name="能力绑定|MonsterAbility" sheetId="6" r:id="rIdCfg6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <ns4:calcFeatures>
+        <ns4:feature name="microsoft.com:RD"/>
+        <ns4:feature name="microsoft.com:Single"/>
+        <ns4:feature name="microsoft.com:FV"/>
+        <ns4:feature name="microsoft.com:CNMTM"/>
+        <ns4:feature name="microsoft.com:LET_WF"/>
+        <ns4:feature name="microsoft.com:LAMBDA_WF"/>
+        <ns4:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </ns4:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -624,14 +627,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" ns1:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -856,8 +859,22 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF17344A"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+    </font>
   </fonts>
-  <fills count="39">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1086,8 +1103,19 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8CDE1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1260,8 +1288,9 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1410,8 +1439,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="39" borderId="14"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1489,6 +1519,34 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="39" borderId="14" xfId="50"/>
+    <xf numFmtId="0" fontId="32" fillId="41" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="41" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="41" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="41" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="41" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="39" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="41" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="41" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="39" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="39" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="41" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1736,7 +1794,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" ns2:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1745,7 +1803,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" ns2:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1759,8 +1817,8 @@
     </tableStyle>
   </tableStyles>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1958,6 +2016,594 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/cfg4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="33" t="str">
+        <v>行为ID</v>
+      </c>
+      <c r="B1" s="33" t="str">
+        <v>怪物ID</v>
+      </c>
+      <c r="C1" s="33" t="str">
+        <v>警戒移速 毫米/Tick</v>
+      </c>
+      <c r="D1" s="33" t="str">
+        <v>脱战延迟 Tick</v>
+      </c>
+      <c r="E1" s="33" t="str">
+        <v>减伤 基点</v>
+      </c>
+      <c r="F1" s="33" t="str">
+        <v>允许普攻 0/1</v>
+      </c>
+      <c r="G1" s="33" t="str">
+        <v>狂暴血量阈值 降序|分隔</v>
+      </c>
+      <c r="H1" s="33" t="str">
+        <v>狂暴时长 Tick</v>
+      </c>
+      <c r="I1" s="33" t="str">
+        <v>狂暴触发能力ID 无填0</v>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="33" t="str">
+        <v>int32</v>
+      </c>
+      <c r="B2" s="33" t="str">
+        <v>int32</v>
+      </c>
+      <c r="C2" s="33" t="str">
+        <v>int32</v>
+      </c>
+      <c r="D2" s="33" t="str">
+        <v>int32</v>
+      </c>
+      <c r="E2" s="33" t="str">
+        <v>int32</v>
+      </c>
+      <c r="F2" s="33" t="str">
+        <v>int32</v>
+      </c>
+      <c r="G2" s="33" t="str">
+        <v>string</v>
+      </c>
+      <c r="H2" s="33" t="str">
+        <v>int32</v>
+      </c>
+      <c r="I2" s="33" t="str">
+        <v>int32</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="33" t="str">
+        <v>AiIdx</v>
+      </c>
+      <c r="B3" s="33" t="str">
+        <v>MonsterIdx</v>
+      </c>
+      <c r="C3" s="33" t="str">
+        <v>AlertSpeed</v>
+      </c>
+      <c r="D3" s="33" t="str">
+        <v>DisengageTicks</v>
+      </c>
+      <c r="E3" s="33" t="str">
+        <v>DamageReductionBp</v>
+      </c>
+      <c r="F3" s="33" t="str">
+        <v>Basic</v>
+      </c>
+      <c r="G3" s="33" t="str">
+        <v>RageThresholds</v>
+      </c>
+      <c r="H3" s="33" t="str">
+        <v>RageTicks</v>
+      </c>
+      <c r="I3" s="33" t="str">
+        <v>RageAbilityIdx</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="33" t="str">
+        <v>server/client/key</v>
+      </c>
+      <c r="B4" s="33" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="C4" s="33" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="D4" s="33" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="E4" s="33" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="F4" s="33" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="G4" s="33" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="H4" s="33" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="I4" s="33" t="str">
+        <v>server/client</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="34"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="34"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="34"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="34"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="34"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="34"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/cfg5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="33" t="str">
+        <v>能力ID</v>
+      </c>
+      <c r="B1" s="33" t="str">
+        <v>类型 melee/summon</v>
+      </c>
+      <c r="C1" s="33" t="str">
+        <v>作用距离 毫米</v>
+      </c>
+      <c r="D1" s="33" t="str">
+        <v>伤害</v>
+      </c>
+      <c r="E1" s="33" t="str">
+        <v>前摇 Tick</v>
+      </c>
+      <c r="F1" s="33" t="str">
+        <v>后摇 Tick</v>
+      </c>
+      <c r="G1" s="33" t="str">
+        <v>冷却 Tick</v>
+      </c>
+      <c r="H1" s="33" t="str">
+        <v>召唤怪ID 无填0</v>
+      </c>
+      <c r="I1" s="33" t="str">
+        <v>双圈外消失延迟 Tick</v>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="33" t="str">
+        <v>int32</v>
+      </c>
+      <c r="B2" s="33" t="str">
+        <v>string</v>
+      </c>
+      <c r="C2" s="33" t="str">
+        <v>int32</v>
+      </c>
+      <c r="D2" s="33" t="str">
+        <v>int32</v>
+      </c>
+      <c r="E2" s="33" t="str">
+        <v>int32</v>
+      </c>
+      <c r="F2" s="33" t="str">
+        <v>int32</v>
+      </c>
+      <c r="G2" s="33" t="str">
+        <v>int32</v>
+      </c>
+      <c r="H2" s="33" t="str">
+        <v>int32</v>
+      </c>
+      <c r="I2" s="33" t="str">
+        <v>int32</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="33" t="str">
+        <v>AbilityIdx</v>
+      </c>
+      <c r="B3" s="33" t="str">
+        <v>Kind</v>
+      </c>
+      <c r="C3" s="33" t="str">
+        <v>Range</v>
+      </c>
+      <c r="D3" s="33" t="str">
+        <v>Damage</v>
+      </c>
+      <c r="E3" s="33" t="str">
+        <v>WindupTicks</v>
+      </c>
+      <c r="F3" s="33" t="str">
+        <v>RecoveryTicks</v>
+      </c>
+      <c r="G3" s="33" t="str">
+        <v>CooldownTicks</v>
+      </c>
+      <c r="H3" s="33" t="str">
+        <v>SummonMonsterIdx</v>
+      </c>
+      <c r="I3" s="33" t="str">
+        <v>DespawnTicks</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="33" t="str">
+        <v>server/client/key</v>
+      </c>
+      <c r="B4" s="33" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="C4" s="33" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="D4" s="33" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="E4" s="33" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="F4" s="33" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="G4" s="33" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="H4" s="33" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="I4" s="33" t="str">
+        <v>server/client</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="34"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="34"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="34"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="34"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="34"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="34"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/cfg6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="33" t="str">
+        <v>绑定ID</v>
+      </c>
+      <c r="B1" s="33" t="str">
+        <v>怪物ID</v>
+      </c>
+      <c r="C1" s="33" t="str">
+        <v>能力ID</v>
+      </c>
+      <c r="D1" s="33" t="str">
+        <v>阶段 alert/rage</v>
+      </c>
+      <c r="E1" s="33" t="str">
+        <v>优先级 小值优先</v>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="33" t="str">
+        <v>int32</v>
+      </c>
+      <c r="B2" s="33" t="str">
+        <v>int32</v>
+      </c>
+      <c r="C2" s="33" t="str">
+        <v>int32</v>
+      </c>
+      <c r="D2" s="33" t="str">
+        <v>string</v>
+      </c>
+      <c r="E2" s="33" t="str">
+        <v>int32</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="33" t="str">
+        <v>BindIdx</v>
+      </c>
+      <c r="B3" s="33" t="str">
+        <v>MonsterIdx</v>
+      </c>
+      <c r="C3" s="33" t="str">
+        <v>AbilityIdx</v>
+      </c>
+      <c r="D3" s="33" t="str">
+        <v>Phase</v>
+      </c>
+      <c r="E3" s="33" t="str">
+        <v>Priority</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="33" t="str">
+        <v>server/client/key</v>
+      </c>
+      <c r="B4" s="33" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="C4" s="33" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="D4" s="33" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="E4" s="33" t="str">
+        <v>server/client</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="34"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="34"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="34"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="34"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="34"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="34"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>

--- a/design/怪物表.xlsx
+++ b/design/怪物表.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <ns1:AlternateContent>
-    <ns1:Choice Requires="x15">
+  <mc:AlternateContent>
+    <mc:Choice Requires="x15">
       <ns2:absPath url="E:\聚光灯\Hunter\design\"/>
-    </ns1:Choice>
-  </ns1:AlternateContent>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="24750" windowHeight="12060"/>
   </bookViews>
   <sheets>
     <sheet name="怪物|Monster" sheetId="1" r:id="rId1"/>
-    <sheet name="怪物技能|MonsterSkill" sheetId="2" r:id="rId2"/>
+    <sheet name="怪物技能历史说明" sheetId="2" r:id="rId2"/>
     <sheet name="招式|Attack" sheetId="3" r:id="rId3"/>
     <sheet name="怪物行为|MonsterAi" sheetId="4" r:id="rIdCfg4"/>
     <sheet name="能力|Ability" sheetId="5" r:id="rIdCfg5"/>
@@ -634,7 +634,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="65">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -873,8 +873,171 @@
       <sz val="11"/>
       <name val="Microsoft YaHei"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF20364D"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF12283F"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF79511F"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF79511F"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF202C3A"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF20364D"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF20364D"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF20364D"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="42">
+  <fills count="79">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1114,8 +1277,193 @@
         <fgColor rgb="FFB8CDE1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD3E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9CEE3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF0CF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1289,8 +1637,145 @@
       <diagonal/>
     </border>
     <border/>
+    <border>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7EFF7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7EFF7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7EFF7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7EFF7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color theme="4" tint="0.49998"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+    </border>
   </borders>
-  <cellStyleXfs count="51">
+  <cellStyleXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1440,8 +1925,155 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="32" fillId="39" borderId="14"/>
+    <xf numFmtId="0" fontId="32" fillId="39" borderId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="42" fillId="39" borderId="14" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="42" fillId="39" borderId="14" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="42" fillId="39" borderId="14" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="42" fillId="39" borderId="14" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="42" fillId="39" borderId="14" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="39" borderId="14" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="39" borderId="14" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="48" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="39" borderId="14" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="39" borderId="14" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="39" borderId="14" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="39" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="39" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="39" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="39" borderId="14" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="49" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="50" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="50" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="51" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="39" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="39" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="52" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="53" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="54" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="55" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="56" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="57" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="58" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="59" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="60" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="61" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="62" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="63" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="64" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="65" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="66" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="67" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="68" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="69" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="70" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="71" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="72" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="73" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="74" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="75" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="76" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="77" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="78" borderId="14" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1547,6 +2179,91 @@
     </xf>
     <xf numFmtId="0" fontId="34" fillId="41" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="42" borderId="14" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="39" borderId="14" xfId="50" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="43" borderId="15" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="43" borderId="16" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="44" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="43" borderId="17" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="43" borderId="18" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="39" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="39" fillId="45" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="39" fillId="46" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="32" fillId="39" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="39" borderId="19" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="43" borderId="19" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="47" borderId="19" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="42" borderId="14" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="43" borderId="19" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="47" borderId="19" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="42" borderId="14" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="39" fillId="45" borderId="19" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="45" borderId="19" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="39" borderId="14" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="39" fillId="46" borderId="19" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="46" borderId="19" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="34" fillId="39" borderId="19" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="39" borderId="19" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="34" fillId="39" borderId="19" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="39" borderId="19" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="42" borderId="14" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="64" fillId="42" borderId="14" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="64" fillId="42" borderId="14" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="42" borderId="14" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -2148,81 +2865,197 @@
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="34"/>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
+      <c r="A5" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="D5" s="34" t="n">
+        <v>120</v>
+      </c>
+      <c r="E5" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="34" t="str"/>
+      <c r="H5" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="34"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
+      <c r="A6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="34" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" s="34" t="n">
+        <v>120</v>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="34" t="str"/>
+      <c r="H6" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="34"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
+      <c r="A7" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="D7" s="34" t="n">
+        <v>120</v>
+      </c>
+      <c r="E7" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="34" t="str"/>
+      <c r="H7" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="34"/>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
+      <c r="A8" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="D8" s="34" t="n">
+        <v>120</v>
+      </c>
+      <c r="E8" s="34" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F8" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="34" t="str"/>
+      <c r="H8" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="34"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
+      <c r="A9" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="34" t="n">
+        <v>55</v>
+      </c>
+      <c r="D9" s="34" t="n">
+        <v>120</v>
+      </c>
+      <c r="E9" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="34" t="str">
+        <v>400|200</v>
+      </c>
+      <c r="H9" s="34" t="n">
+        <v>180</v>
+      </c>
+      <c r="I9" s="34" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="34"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
+      <c r="A10" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="34" t="n">
+        <v>1002</v>
+      </c>
+      <c r="C10" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="D10" s="34" t="n">
+        <v>120</v>
+      </c>
+      <c r="E10" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="34" t="str"/>
+      <c r="H10" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="34"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
+      <c r="A11" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="34" t="n">
+        <v>1003</v>
+      </c>
+      <c r="C11" s="34" t="n">
+        <v>40</v>
+      </c>
+      <c r="D11" s="34" t="n">
+        <v>120</v>
+      </c>
+      <c r="E11" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="34" t="str">
+        <v>160|80</v>
+      </c>
+      <c r="H11" s="34" t="n">
+        <v>180</v>
+      </c>
+      <c r="I11" s="34" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="34"/>
@@ -2372,37 +3205,91 @@
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="34"/>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
+      <c r="A5" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="34" t="str">
+        <v>melee</v>
+      </c>
+      <c r="C5" s="34" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D5" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="E5" s="34" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" s="34" t="n">
+        <v>15</v>
+      </c>
+      <c r="G5" s="34" t="n">
+        <v>120</v>
+      </c>
+      <c r="H5" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="34"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
+      <c r="A6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="34" t="str">
+        <v>melee</v>
+      </c>
+      <c r="C6" s="34" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D6" s="34" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>18</v>
+      </c>
+      <c r="G6" s="34" t="n">
+        <v>90</v>
+      </c>
+      <c r="H6" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="34"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
+      <c r="A7" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="34" t="str">
+        <v>summon</v>
+      </c>
+      <c r="C7" s="34" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D7" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="34" t="n">
+        <v>30</v>
+      </c>
+      <c r="F7" s="34" t="n">
+        <v>15</v>
+      </c>
+      <c r="G7" s="34" t="n">
+        <v>180</v>
+      </c>
+      <c r="H7" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="34" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="34"/>
@@ -2544,39 +3431,89 @@
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="34"/>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
+      <c r="A5" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="34" t="str">
+        <v>alert</v>
+      </c>
+      <c r="E5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="34"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
+      <c r="A6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="34" t="str">
+        <v>alert</v>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="34"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
+      <c r="A7" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="34" t="str">
+        <v>rage</v>
+      </c>
+      <c r="E7" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="34"/>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
+      <c r="A8" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="34" t="n">
+        <v>1003</v>
+      </c>
+      <c r="C8" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="34" t="str">
+        <v>alert</v>
+      </c>
+      <c r="E8" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="34"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
+      <c r="A9" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="34" t="n">
+        <v>1003</v>
+      </c>
+      <c r="C9" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="34" t="str">
+        <v>rage</v>
+      </c>
+      <c r="E9" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="34"/>
@@ -2609,7 +3546,7 @@
   <sheetPr>
     <tabColor rgb="FF577A9A"/>
   </sheetPr>
-  <dimension ref="A1:U504"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="20" style="12" customWidth="1"/>
@@ -2622,6 +3559,7 @@
     <col min="13" max="14" width="13.5" style="12" customWidth="1"/>
     <col min="15" max="15" width="9.5" style="12" customWidth="1"/>
     <col min="16" max="17" width="22" customWidth="1"/>
+    <col min="18" max="18" width="22" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:21">
@@ -2676,6 +3614,9 @@
       <c r="Q1" s="15" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="70" t="str">
+        <v>运行启用（0/1）</v>
+      </c>
       <c r="U1" t="s">
         <v>17</v>
       </c>
@@ -2732,6 +3673,9 @@
       <c r="Q2" s="18" t="s">
         <v>18</v>
       </c>
+      <c r="R2" s="70" t="str">
+        <v>int32</v>
+      </c>
       <c r="U2" t="s">
         <v>20</v>
       </c>
@@ -2788,6 +3732,9 @@
       <c r="Q3" s="18" t="s">
         <v>37</v>
       </c>
+      <c r="R3" s="70" t="str">
+        <v>Enabled</v>
+      </c>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:21">
       <c r="A4" s="16" t="s">
@@ -2841,6 +3788,9 @@
       <c r="Q4" s="18" t="s">
         <v>39</v>
       </c>
+      <c r="R4" s="70" t="str">
+        <v>server/client</v>
+      </c>
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:21">
       <c r="A5" s="19">
@@ -2861,9 +3811,15 @@
       <c r="F5" s="19">
         <v>60</v>
       </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
+      <c r="G5" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="58" t="n">
+        <v>0</v>
+      </c>
       <c r="J5" s="19">
         <v>35</v>
       </c>
@@ -2873,13 +3829,26 @@
       <c r="L5" s="19">
         <v>6000</v>
       </c>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="21"/>
+      <c r="M5" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="59" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="P5" s="41" t="n">
+        <v>1002</v>
+      </c>
+      <c r="Q5" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
       <c r="U5" t="s">
         <v>43</v>
       </c>
@@ -2903,9 +3872,15 @@
       <c r="F6" s="22">
         <v>126</v>
       </c>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
+      <c r="G6" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="61" t="n">
+        <v>0</v>
+      </c>
       <c r="J6" s="22">
         <v>20</v>
       </c>
@@ -2915,11 +3890,22 @@
       <c r="L6" s="22">
         <v>6000</v>
       </c>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
+      <c r="M6" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="62" t="n">
+        <v>0</v>
+      </c>
       <c r="O6" s="23"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
+      <c r="P6" s="41" t="n">
+        <v>1002</v>
+      </c>
+      <c r="Q6" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" ht="26" customHeight="1" spans="1:21">
       <c r="A7" s="19">
@@ -2928,8 +3914,8 @@
       <c r="B7" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="19">
-        <v>3</v>
+      <c r="C7" s="58" t="n">
+        <v>4</v>
       </c>
       <c r="D7" s="19">
         <v>300</v>
@@ -2937,12 +3923,18 @@
       <c r="E7" s="19">
         <v>700</v>
       </c>
-      <c r="F7" s="19">
-        <v>150</v>
-      </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
+      <c r="F7" s="58" t="n">
+        <v>30</v>
+      </c>
+      <c r="G7" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="58" t="n">
+        <v>0</v>
+      </c>
       <c r="J7" s="19">
         <v>50</v>
       </c>
@@ -2952,11 +3944,22 @@
       <c r="L7" s="19">
         <v>6000</v>
       </c>
-      <c r="M7" s="20"/>
-      <c r="N7" s="20"/>
+      <c r="M7" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="59" t="n">
+        <v>0</v>
+      </c>
       <c r="O7" s="20"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
+      <c r="P7" s="41" t="n">
+        <v>1002</v>
+      </c>
+      <c r="Q7" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" ht="26" customHeight="1" spans="1:21">
       <c r="A8" s="22">
@@ -2977,9 +3980,15 @@
       <c r="F8" s="22">
         <v>150</v>
       </c>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
+      <c r="G8" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="61" t="n">
+        <v>0</v>
+      </c>
       <c r="J8" s="22">
         <v>35</v>
       </c>
@@ -2989,11 +3998,22 @@
       <c r="L8" s="22">
         <v>6000</v>
       </c>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
+      <c r="M8" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="62" t="n">
+        <v>0</v>
+      </c>
       <c r="O8" s="23"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
+      <c r="P8" s="41" t="n">
+        <v>1002</v>
+      </c>
+      <c r="Q8" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" ht="26" customHeight="1" spans="1:21">
       <c r="A9" s="19">
@@ -3002,8 +4022,8 @@
       <c r="B9" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="19">
-        <v>4</v>
+      <c r="C9" s="58" t="n">
+        <v>3</v>
       </c>
       <c r="D9" s="19">
         <v>1000</v>
@@ -3014,9 +4034,15 @@
       <c r="F9" s="19">
         <v>600</v>
       </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
+      <c r="G9" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="58" t="n">
+        <v>0</v>
+      </c>
       <c r="J9" s="19">
         <v>45</v>
       </c>
@@ -3026,53 +4052,130 @@
       <c r="L9" s="19">
         <v>6000</v>
       </c>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
+      <c r="M9" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="59" t="n">
+        <v>0</v>
+      </c>
       <c r="O9" s="20"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
+      <c r="P9" s="41" t="n">
+        <v>1003</v>
+      </c>
+      <c r="Q9" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" ht="26" customHeight="1" spans="1:21">
       <c r="A10" s="22">
         <v>6</v>
       </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
+      <c r="B10" s="62" t="str">
+        <v>预留怪物6</v>
+      </c>
+      <c r="C10" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="62" t="n">
+        <v>0</v>
+      </c>
       <c r="O10" s="23"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
+      <c r="P10" s="41" t="n">
+        <v>1002</v>
+      </c>
+      <c r="Q10" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" ht="26" customHeight="1" spans="1:21">
       <c r="A11" s="19">
         <v>7</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="20"/>
+      <c r="B11" s="59" t="str">
+        <v>预留怪物7</v>
+      </c>
+      <c r="C11" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="59" t="n">
+        <v>0</v>
+      </c>
       <c r="O11" s="20"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
+      <c r="P11" s="41" t="n">
+        <v>1002</v>
+      </c>
+      <c r="Q11" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:21">
       <c r="A12" s="24">
@@ -3117,13 +4220,18 @@
       <c r="N12" s="25">
         <v>0</v>
       </c>
-      <c r="O12" s="25" t="s">
-        <v>42</v>
+      <c r="O12" s="64" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="P12" s="2">
         <v>1002</v>
       </c>
       <c r="Q12" s="2">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3170,14 +4278,19 @@
       <c r="N13" s="25">
         <v>0</v>
       </c>
-      <c r="O13" s="25" t="s">
-        <v>42</v>
+      <c r="O13" s="64" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="P13" s="2">
         <v>1003</v>
       </c>
       <c r="Q13" s="2">
         <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:21">
